--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_Auto_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_Auto_Fiets.xlsx
@@ -510,7 +510,7 @@
         <v>2196</v>
       </c>
       <c r="D9">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="E9">
         <v>2200</v>
@@ -524,13 +524,13 @@
         <v>2048</v>
       </c>
       <c r="C10">
-        <v>2084</v>
+        <v>2087</v>
       </c>
       <c r="D10">
-        <v>2130</v>
+        <v>2137</v>
       </c>
       <c r="E10">
-        <v>2152</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2038</v>
+        <v>2046</v>
       </c>
       <c r="C11">
-        <v>2088</v>
+        <v>2102</v>
       </c>
       <c r="D11">
-        <v>2138</v>
+        <v>2146</v>
       </c>
       <c r="E11">
-        <v>2159</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -558,13 +558,13 @@
         <v>1810</v>
       </c>
       <c r="C12">
-        <v>1920</v>
+        <v>1941</v>
       </c>
       <c r="D12">
-        <v>2039</v>
+        <v>2056</v>
       </c>
       <c r="E12">
-        <v>2096</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -575,13 +575,13 @@
         <v>2016</v>
       </c>
       <c r="C13">
-        <v>2060</v>
+        <v>2063</v>
       </c>
       <c r="D13">
-        <v>2115</v>
+        <v>2124</v>
       </c>
       <c r="E13">
-        <v>2142</v>
+        <v>2144</v>
       </c>
     </row>
   </sheetData>
